--- a/Shiny/Datos limpios/pricing_diario_historico_sorgo.xlsx
+++ b/Shiny/Datos limpios/pricing_diario_historico_sorgo.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2869"/>
+  <dimension ref="A1:K2889"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -106317,16 +106317,16 @@
         <v>45947</v>
       </c>
       <c r="B2864">
-        <v>18404.82</v>
+        <v>17904.82</v>
       </c>
       <c r="C2864">
         <v>0</v>
       </c>
       <c r="D2864">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E2864">
-        <v>18404.82</v>
+        <v>17404.82</v>
       </c>
       <c r="F2864">
         <v>60.13</v>
@@ -106341,7 +106341,7 @@
         <v>60.13</v>
       </c>
       <c r="J2864">
-        <v>18464.95</v>
+        <v>17464.95</v>
       </c>
       <c r="K2864" t="inlineStr">
         <is>
@@ -106529,6 +106529,746 @@
         <v>684.49</v>
       </c>
       <c r="K2869" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2870">
+      <c r="A2870" s="2">
+        <v>45957</v>
+      </c>
+      <c r="B2870">
+        <v>775</v>
+      </c>
+      <c r="C2870">
+        <v>0</v>
+      </c>
+      <c r="D2870">
+        <v>0</v>
+      </c>
+      <c r="E2870">
+        <v>775</v>
+      </c>
+      <c r="F2870">
+        <v>514.08</v>
+      </c>
+      <c r="G2870">
+        <v>0</v>
+      </c>
+      <c r="H2870">
+        <v>0</v>
+      </c>
+      <c r="I2870">
+        <v>514.08</v>
+      </c>
+      <c r="J2870">
+        <v>1289.08</v>
+      </c>
+      <c r="K2870" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2871">
+      <c r="A2871" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B2871">
+        <v>1520.12</v>
+      </c>
+      <c r="C2871">
+        <v>0</v>
+      </c>
+      <c r="D2871">
+        <v>0</v>
+      </c>
+      <c r="E2871">
+        <v>1520.12</v>
+      </c>
+      <c r="F2871">
+        <v>36</v>
+      </c>
+      <c r="G2871">
+        <v>0</v>
+      </c>
+      <c r="H2871">
+        <v>0</v>
+      </c>
+      <c r="I2871">
+        <v>36</v>
+      </c>
+      <c r="J2871">
+        <v>1556.12</v>
+      </c>
+      <c r="K2871" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2872">
+      <c r="A2872" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B2872">
+        <v>164.4</v>
+      </c>
+      <c r="C2872">
+        <v>0.7799999999999999</v>
+      </c>
+      <c r="D2872">
+        <v>0.7799999999999999</v>
+      </c>
+      <c r="E2872">
+        <v>164.4</v>
+      </c>
+      <c r="F2872">
+        <v>1500</v>
+      </c>
+      <c r="G2872">
+        <v>0</v>
+      </c>
+      <c r="H2872">
+        <v>0</v>
+      </c>
+      <c r="I2872">
+        <v>1500</v>
+      </c>
+      <c r="J2872">
+        <v>1664.4</v>
+      </c>
+      <c r="K2872" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2873">
+      <c r="A2873" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B2873">
+        <v>561.78</v>
+      </c>
+      <c r="C2873">
+        <v>0</v>
+      </c>
+      <c r="D2873">
+        <v>0</v>
+      </c>
+      <c r="E2873">
+        <v>561.78</v>
+      </c>
+      <c r="F2873">
+        <v>330.28</v>
+      </c>
+      <c r="G2873">
+        <v>0</v>
+      </c>
+      <c r="H2873">
+        <v>0</v>
+      </c>
+      <c r="I2873">
+        <v>330.28</v>
+      </c>
+      <c r="J2873">
+        <v>892.0599999999999</v>
+      </c>
+      <c r="K2873" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2874">
+      <c r="A2874" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B2874">
+        <v>1686.36</v>
+      </c>
+      <c r="C2874">
+        <v>59.08</v>
+      </c>
+      <c r="D2874">
+        <v>0</v>
+      </c>
+      <c r="E2874">
+        <v>1745.44</v>
+      </c>
+      <c r="F2874">
+        <v>6214.9</v>
+      </c>
+      <c r="G2874">
+        <v>0</v>
+      </c>
+      <c r="H2874">
+        <v>300</v>
+      </c>
+      <c r="I2874">
+        <v>5914.9</v>
+      </c>
+      <c r="J2874">
+        <v>7660.339999999999</v>
+      </c>
+      <c r="K2874" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2875">
+      <c r="A2875" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B2875">
+        <v>579.28</v>
+      </c>
+      <c r="C2875">
+        <v>0</v>
+      </c>
+      <c r="D2875">
+        <v>0</v>
+      </c>
+      <c r="E2875">
+        <v>579.28</v>
+      </c>
+      <c r="F2875">
+        <v>2120</v>
+      </c>
+      <c r="G2875">
+        <v>0</v>
+      </c>
+      <c r="H2875">
+        <v>0</v>
+      </c>
+      <c r="I2875">
+        <v>2120</v>
+      </c>
+      <c r="J2875">
+        <v>2699.28</v>
+      </c>
+      <c r="K2875" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2876">
+      <c r="A2876" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B2876">
+        <v>895.99</v>
+      </c>
+      <c r="C2876">
+        <v>0</v>
+      </c>
+      <c r="D2876">
+        <v>0</v>
+      </c>
+      <c r="E2876">
+        <v>895.99</v>
+      </c>
+      <c r="F2876">
+        <v>814.16</v>
+      </c>
+      <c r="G2876">
+        <v>0</v>
+      </c>
+      <c r="H2876">
+        <v>0</v>
+      </c>
+      <c r="I2876">
+        <v>814.16</v>
+      </c>
+      <c r="J2876">
+        <v>1710.15</v>
+      </c>
+      <c r="K2876" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2877">
+      <c r="A2877" s="2">
+        <v>45966</v>
+      </c>
+      <c r="B2877">
+        <v>1036.88</v>
+      </c>
+      <c r="C2877">
+        <v>500</v>
+      </c>
+      <c r="D2877">
+        <v>30</v>
+      </c>
+      <c r="E2877">
+        <v>1506.88</v>
+      </c>
+      <c r="F2877">
+        <v>3121.38</v>
+      </c>
+      <c r="G2877">
+        <v>0</v>
+      </c>
+      <c r="H2877">
+        <v>0</v>
+      </c>
+      <c r="I2877">
+        <v>3121.38</v>
+      </c>
+      <c r="J2877">
+        <v>4628.26</v>
+      </c>
+      <c r="K2877" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2878">
+      <c r="A2878" s="2">
+        <v>45967</v>
+      </c>
+      <c r="B2878">
+        <v>804.12</v>
+      </c>
+      <c r="C2878">
+        <v>11.44</v>
+      </c>
+      <c r="D2878">
+        <v>0</v>
+      </c>
+      <c r="E2878">
+        <v>815.5600000000001</v>
+      </c>
+      <c r="F2878">
+        <v>1130.72</v>
+      </c>
+      <c r="G2878">
+        <v>0</v>
+      </c>
+      <c r="H2878">
+        <v>0</v>
+      </c>
+      <c r="I2878">
+        <v>1130.72</v>
+      </c>
+      <c r="J2878">
+        <v>1946.28</v>
+      </c>
+      <c r="K2878" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2879">
+      <c r="A2879" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B2879">
+        <v>1359.89</v>
+      </c>
+      <c r="C2879">
+        <v>0</v>
+      </c>
+      <c r="D2879">
+        <v>0</v>
+      </c>
+      <c r="E2879">
+        <v>1359.89</v>
+      </c>
+      <c r="F2879">
+        <v>849.1900000000001</v>
+      </c>
+      <c r="G2879">
+        <v>0</v>
+      </c>
+      <c r="H2879">
+        <v>0</v>
+      </c>
+      <c r="I2879">
+        <v>849.1900000000001</v>
+      </c>
+      <c r="J2879">
+        <v>2209.08</v>
+      </c>
+      <c r="K2879" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2880">
+      <c r="A2880" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B2880">
+        <v>1321.14</v>
+      </c>
+      <c r="C2880">
+        <v>0</v>
+      </c>
+      <c r="D2880">
+        <v>0</v>
+      </c>
+      <c r="E2880">
+        <v>1321.14</v>
+      </c>
+      <c r="F2880">
+        <v>700</v>
+      </c>
+      <c r="G2880">
+        <v>0</v>
+      </c>
+      <c r="H2880">
+        <v>0</v>
+      </c>
+      <c r="I2880">
+        <v>700</v>
+      </c>
+      <c r="J2880">
+        <v>2021.14</v>
+      </c>
+      <c r="K2880" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2881">
+      <c r="A2881" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B2881">
+        <v>797.55</v>
+      </c>
+      <c r="C2881">
+        <v>0</v>
+      </c>
+      <c r="D2881">
+        <v>0</v>
+      </c>
+      <c r="E2881">
+        <v>797.55</v>
+      </c>
+      <c r="F2881">
+        <v>640</v>
+      </c>
+      <c r="G2881">
+        <v>0</v>
+      </c>
+      <c r="H2881">
+        <v>0</v>
+      </c>
+      <c r="I2881">
+        <v>640</v>
+      </c>
+      <c r="J2881">
+        <v>1437.55</v>
+      </c>
+      <c r="K2881" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2882">
+      <c r="A2882" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B2882">
+        <v>641.79</v>
+      </c>
+      <c r="C2882">
+        <v>106.67</v>
+      </c>
+      <c r="D2882">
+        <v>0</v>
+      </c>
+      <c r="E2882">
+        <v>748.4599999999999</v>
+      </c>
+      <c r="F2882">
+        <v>330</v>
+      </c>
+      <c r="G2882">
+        <v>0</v>
+      </c>
+      <c r="H2882">
+        <v>0</v>
+      </c>
+      <c r="I2882">
+        <v>330</v>
+      </c>
+      <c r="J2882">
+        <v>1078.46</v>
+      </c>
+      <c r="K2882" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2883">
+      <c r="A2883" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B2883">
+        <v>1177.18</v>
+      </c>
+      <c r="C2883">
+        <v>0</v>
+      </c>
+      <c r="D2883">
+        <v>0</v>
+      </c>
+      <c r="E2883">
+        <v>1177.18</v>
+      </c>
+      <c r="F2883">
+        <v>704.3</v>
+      </c>
+      <c r="G2883">
+        <v>0</v>
+      </c>
+      <c r="H2883">
+        <v>0</v>
+      </c>
+      <c r="I2883">
+        <v>704.3</v>
+      </c>
+      <c r="J2883">
+        <v>1881.48</v>
+      </c>
+      <c r="K2883" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2884">
+      <c r="A2884" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B2884">
+        <v>847.15</v>
+      </c>
+      <c r="C2884">
+        <v>0</v>
+      </c>
+      <c r="D2884">
+        <v>0</v>
+      </c>
+      <c r="E2884">
+        <v>847.15</v>
+      </c>
+      <c r="F2884">
+        <v>330</v>
+      </c>
+      <c r="G2884">
+        <v>0</v>
+      </c>
+      <c r="H2884">
+        <v>0</v>
+      </c>
+      <c r="I2884">
+        <v>330</v>
+      </c>
+      <c r="J2884">
+        <v>1177.15</v>
+      </c>
+      <c r="K2884" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2885">
+      <c r="A2885" s="2">
+        <v>45976</v>
+      </c>
+      <c r="B2885">
+        <v>145</v>
+      </c>
+      <c r="C2885">
+        <v>0</v>
+      </c>
+      <c r="D2885">
+        <v>0</v>
+      </c>
+      <c r="E2885">
+        <v>145</v>
+      </c>
+      <c r="F2885">
+        <v>0</v>
+      </c>
+      <c r="G2885">
+        <v>0</v>
+      </c>
+      <c r="H2885">
+        <v>0</v>
+      </c>
+      <c r="I2885">
+        <v>0</v>
+      </c>
+      <c r="J2885">
+        <v>145</v>
+      </c>
+      <c r="K2885" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2886">
+      <c r="A2886" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B2886">
+        <v>473.95</v>
+      </c>
+      <c r="C2886">
+        <v>0</v>
+      </c>
+      <c r="D2886">
+        <v>0</v>
+      </c>
+      <c r="E2886">
+        <v>473.95</v>
+      </c>
+      <c r="F2886">
+        <v>270</v>
+      </c>
+      <c r="G2886">
+        <v>0</v>
+      </c>
+      <c r="H2886">
+        <v>0</v>
+      </c>
+      <c r="I2886">
+        <v>270</v>
+      </c>
+      <c r="J2886">
+        <v>743.95</v>
+      </c>
+      <c r="K2886" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2887">
+      <c r="A2887" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B2887">
+        <v>420</v>
+      </c>
+      <c r="C2887">
+        <v>0</v>
+      </c>
+      <c r="D2887">
+        <v>0</v>
+      </c>
+      <c r="E2887">
+        <v>420</v>
+      </c>
+      <c r="F2887">
+        <v>60</v>
+      </c>
+      <c r="G2887">
+        <v>0</v>
+      </c>
+      <c r="H2887">
+        <v>0</v>
+      </c>
+      <c r="I2887">
+        <v>60</v>
+      </c>
+      <c r="J2887">
+        <v>480</v>
+      </c>
+      <c r="K2887" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2888">
+      <c r="A2888" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B2888">
+        <v>332.46</v>
+      </c>
+      <c r="C2888">
+        <v>0</v>
+      </c>
+      <c r="D2888">
+        <v>0</v>
+      </c>
+      <c r="E2888">
+        <v>332.46</v>
+      </c>
+      <c r="F2888">
+        <v>130</v>
+      </c>
+      <c r="G2888">
+        <v>0</v>
+      </c>
+      <c r="H2888">
+        <v>0</v>
+      </c>
+      <c r="I2888">
+        <v>130</v>
+      </c>
+      <c r="J2888">
+        <v>462.46</v>
+      </c>
+      <c r="K2888" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2889">
+      <c r="A2889" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B2889">
+        <v>1364.39</v>
+      </c>
+      <c r="C2889">
+        <v>120</v>
+      </c>
+      <c r="D2889">
+        <v>0</v>
+      </c>
+      <c r="E2889">
+        <v>1484.39</v>
+      </c>
+      <c r="F2889">
+        <v>543.34</v>
+      </c>
+      <c r="G2889">
+        <v>0</v>
+      </c>
+      <c r="H2889">
+        <v>0</v>
+      </c>
+      <c r="I2889">
+        <v>543.34</v>
+      </c>
+      <c r="J2889">
+        <v>2027.73</v>
+      </c>
+      <c r="K2889" t="inlineStr">
         <is>
           <t>SORGO</t>
         </is>
